--- a/AAII_Financials/Yearly/WFF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WFF_YR_FIN.xlsx
@@ -876,7 +876,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -906,7 +906,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -947,7 +947,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8900</v>
+        <v>8700</v>
       </c>
       <c r="E17" s="3">
         <v>4500</v>
@@ -977,7 +977,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1500</v>
+        <v>-1300</v>
       </c>
       <c r="E18" s="3">
         <v>100</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1200</v>
+        <v>-1100</v>
       </c>
       <c r="E21" s="3">
         <v>200</v>
@@ -1594,7 +1594,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
         <v>200</v>
@@ -1624,7 +1624,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="E43" s="3">
         <v>1800</v>
@@ -2708,7 +2708,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
